--- a/02_加值成品/生物/生物8-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物8-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物8-3 生物多樣性與保育　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國一(七年級) 生物8-3 生物多樣性與保育　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>生物多樣性包含哪三層次？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>基因物種生態系</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>抗病與適應力下降易滅絕</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>食物醫藥等資源</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>無天敵大量繁殖排擠原生種</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>三層</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>破壞棲地會威脅？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>復育</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>有害</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>保育</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>生物多樣性</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>威脅</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>無天敵大量繁殖排擠原生種的是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>人人有責</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>有害</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>外來種</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>生物多樣性</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>入侵</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>劃設保護區是為了？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>復育與保護區</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>生物多樣性</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>復育</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>保護</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>生物多樣性能提供人類？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>恢復其族群數量</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>食物醫藥等資源</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>食物醫藥生態服務</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>改變棲地威脅物種</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>資產</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>過度開發對多樣性？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>有害</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>生物多樣性</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>保育</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>人人有責</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>威脅</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>恢復受損族群的行動是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>復育與保護區</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>生物多樣性</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>復育</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>保育</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>復育</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>保育是誰的責任？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>外來種</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>人人有責</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>有害</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>復育與保護區</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>共責</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>基因、物種、生態系三者合稱？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>生物多樣性</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>復育</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>有害</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>外來種</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>三層</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>設立國家公園主要是為了？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>恢復其族群數量</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>食物醫藥等資源</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>改變棲地威脅物種</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>保育生物多樣性</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>保護</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物8-3 生物多樣性與保育　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國一(七年級) 生物8-3 生物多樣性與保育　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>外來種為何造成危害？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>無天敵大量繁殖排擠原生種</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>保育生物多樣性</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>基因物種生態系多樣性維持生態穩定與提供資源</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>造成競爭或排擠</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>入侵</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>氣候變遷對多樣性影響？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>改變棲地威脅物種</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>基因物種生態系多樣性維持生態穩定與提供資源</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>保育生物多樣性</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>造成競爭或排擠</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>變遷</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>生物多樣性的價值舉例？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>基因物種生態系多樣性維持生態穩定與提供資源</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>造成競爭或排擠</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>使用同時不耗竭</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>食物醫藥生態服務</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>價值</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>永續利用資源指？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>食物醫藥等資源</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>基因物種生態系多樣性維持生態穩定與提供資源</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>使用同時不耗竭</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>抗病與適應力下降易滅絕</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>永續</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>汙染如何威脅多樣性？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>保育生物多樣性</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>破壞棲地危害生物</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>生物失去生存空間直接減少</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>缺乏多樣性易被病蟲害全毀</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>汙染</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>基因多樣性的意義？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>減少汙染不購瀕危產品支持永續</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>基因物種生態系</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>增強族群適應與抗病</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>造成競爭或排擠</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>基因</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>福壽螺是本地種還外來種？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>保育</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>復育與保護區</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>外來種</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>復育</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>入侵</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>保育瀕危物種可透過？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>復育與保護區</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>保育</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>外來種</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>復育</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>行動</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>引入強勢外來種對原生種？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>食物醫藥生態服務</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>生物失去生存空間直接減少</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>造成競爭或排擠</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>基因物種生態系</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>入侵</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>復育瀕危物種的目的？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>棲地改變物種來不及適應</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>保護區復育永續利用減汙防外來種</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>食物醫藥等資源</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>恢復其族群數量</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>復育</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物8-3 生物多樣性與保育　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國一(七年級) 生物8-3 生物多樣性與保育　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>說明生物多樣性三層次及其重要性？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>缺乏多樣性易被病蟲害全毀</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>改變棲地威脅物種</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>無天敵大量繁殖排擠原生種</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>基因物種生態系多樣性維持生態穩定與提供資源</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>層次</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>分析外來種入侵如何破壞生態平衡？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>缺乏多樣性易被病蟲害全毀</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>無天敵大量繁殖排擠原生種改變食物網</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>造成競爭或排擠</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>保育生物多樣性</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>入侵</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>為何保育生物多樣性與人類福祉相關？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>提供食物醫藥與生態服務</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>使用同時不耗竭</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>造成競爭或排擠</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>改變棲地威脅物種</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>關聯</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>提出保育生物多樣性的多元策略？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>改變棲地威脅物種</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>基因物種生態系</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>保護區復育永續利用減汙防外來種</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>無天敵大量繁殖排擠原生種</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>策略</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>棲地破壞為何是多樣性最大威脅之一？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>改變棲地威脅物種</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>缺乏多樣性易被病蟲害全毀</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>生物失去生存空間直接減少</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>無天敵大量繁殖排擠原生種改變食物網</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>棲地</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>氣候變遷與生物多樣性喪失的關係？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>基因物種生態系</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>生物失去生存空間直接減少</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>食物醫藥等資源</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>改變棲地與氣候使物種難適應</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>變遷</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>基因多樣性喪失對物種存續的風險？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>抗病與適應力下降易滅絕</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>基因物種生態系</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>改變棲地威脅物種</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>保育生物多樣性</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>風險</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>個人可如何為保育盡力？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>減少汙染不購瀕危產品支持永續</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>無天敵大量繁殖排擠原生種</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>改變棲地威脅物種</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>基因物種生態系</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>行動</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何大面積單一栽培風險高？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>缺乏多樣性易被病蟲害全毀</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>改變棲地威脅物種</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>保育生物多樣性</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>改變棲地與氣候使物種難適應</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>風險</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>氣候變遷如何加劇物種滅絕？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>無天敵大量繁殖排擠原生種</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>生物失去生存空間直接減少</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>增強族群適應與抗病</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>棲地改變物種來不及適應</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>變遷</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/生物/生物8-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物8-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>三層</t>
+          <t>三個層次：生物多樣性包括基因的多樣、物種的多樣，以及生態系類型的多樣</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>威脅</t>
+          <t>失去家園：生物賴以生存的棲地一旦被破壞，很多物種就會失去生存空間而受威脅</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>入侵</t>
+          <t>入侵物種：從外地引進、在當地沒有天敵制衡，因而大量繁殖排擠原生物種的稱外來種</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>保護</t>
+          <t>保護棲地：劃出一塊區域限制開發，讓生物和棲地能受到保護，這就是設保護區的目的</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>資產</t>
+          <t>重要資產：豐富的生物種類能提供人類食物、藥物原料等許多重要資源</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>威脅</t>
+          <t>破壞棲地：過度開發土地會破壞生物的棲息環境，使生物多樣性受到傷害</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>復育</t>
+          <t>幫助恢復：透過人工方式幫助數量減少的物種增加，讓族群恢復健康，稱為復育</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>共責</t>
+          <t>全民參與：保護生物多樣性不只是政府的事，每個人都應該一起盡一份心力</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>三層</t>
+          <t>三層：生物多樣性包含基因多樣性、物種多樣性、生態系多樣性三個層次，合稱生物多樣性</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>保護</t>
+          <t>保護：設立國家公園的主要目的是保護當地的自然環境與野生動植物，維護生物多樣性</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>入侵</t>
+          <t>缺乏制衡：外來種在新環境裡沒有天敵抑制，容易大量繁殖並搶走原生種的生存空間</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>變遷</t>
+          <t>環境改變：氣候變遷會使原本適合生物生存的棲地條件改變，讓許多物種難以適應</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>價值</t>
+          <t>多重價值：生物多樣性能提供人類食物、藥物來源，還能維持乾淨空氣與水等生態服務</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>永續</t>
+          <t>適度使用：一邊使用自然資源，一邊注意不要用光用盡，讓資源能一直被使用下去</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>汙染</t>
+          <t>傷害環境：汙染物會破壞水、土壤等棲地環境，直接危害生活在其中的生物</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>基因</t>
+          <t>提高韌性：同一物種擁有越多不同的基因，越能應付環境變化和抵抗疾病</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>入侵</t>
+          <t>外來引進：福壽螺原本不是台灣本地生物，是被引進後在野外繁殖擴散的外來種</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>行動</t>
+          <t>雙管齊下：透過人工復育增加數量，並設立保護區保護棲地，來幫助瀕危物種</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>入侵</t>
+          <t>入侵：強勢外來種可能與原生物種競爭食物、空間等資源，甚至直接排擠、捕食原生種，威脅原生物種的生存</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>復育</t>
+          <t>復育：復育瀕危物種是希望透過人工繁殖、保護棲地等方式，幫助該物種的族群數量逐漸恢復，避免滅絕</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>層次</t>
+          <t>三層互補：基因、物種、生態系三個層次的多樣性一起維持生態平衡，並提供人類各種資源</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>入侵</t>
+          <t>排擠原生：外來種沒有天敵限制而大量繁殖，搶走原生種的食物和空間，打亂原本的食物網</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>關聯</t>
+          <t>息息相關：人類的糧食、藥物與乾淨環境都仰賴生物多樣性，失去它會直接影響人類生活</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>策略</t>
+          <t>多方並進：設立保護區、進行復育、資源永續利用、減少汙染、防範外來種入侵都是保育方法</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>棲地</t>
+          <t>直接衝擊：棲地一旦被破壞，生物立刻失去生存和繁殖的空間，數量會直接大幅減少</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>變遷</t>
+          <t>間接威脅：氣候變遷改變溫度、雨量等環境條件，讓許多物種來不及適應而數量減少</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>風險</t>
+          <t>風險升高：基因多樣性變少會讓物種抵抗疾病和適應環境變化的能力下降，更容易滅絕</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>行動</t>
+          <t>日常實踐：從減少製造汙染、不購買瀕危物種製品、支持永續產品做起，人人都能盡一份力</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>風險</t>
+          <t>風險：大面積只種植同一種作物，一旦出現適合的病蟲害，因為缺乏基因與物種的多樣性，很容易在短時間內大範圍蔓延，造成整片作物全毀</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>變遷</t>
+          <t>變遷：氣候快速變遷會改變原本的棲地環境（如氣溫、降雨型態），許多物種的演化速度跟不上環境改變的速度，來不及適應就可能走向滅絕</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/生物/生物8-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物8-3_三種難度測驗卷.xlsx
@@ -568,17 +568,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>抗病與適應力下降易滅絕</t>
+          <t>恢復其族群數量</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>食物醫藥等資源</t>
+          <t>生物失去生存空間直接減少</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>無天敵大量繁殖排擠原生種</t>
+          <t>增強族群適應與抗病</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>復育與保護區</t>
+          <t>人人有責</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>生物多樣性</t>
+          <t>保育</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>保育</t>
+          <t>外來種</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1044,17 +1044,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>保育生物多樣性</t>
+          <t>增強族群適應與抗病</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>基因物種生態系多樣性維持生態穩定與提供資源</t>
+          <t>食物醫藥等資源</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>造成競爭或排擠</t>
+          <t>改變棲地威脅物種</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1324,17 +1324,17 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>保育</t>
+          <t>人人有責</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>外來種</t>
+          <t>有害</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>復育</t>
+          <t>生物多樣性</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>缺乏多樣性易被病蟲害全毀</t>
+          <t>食物醫藥等資源</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>無天敵大量繁殖排擠原生種</t>
+          <t>無天敵大量繁殖排擠原生種改變食物網</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>缺乏多樣性易被病蟲害全毀</t>
+          <t>食物醫藥生態服務</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>造成競爭或排擠</t>
+          <t>基因物種生態系</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>保育生物多樣性</t>
+          <t>保護區復育永續利用減汙防外來種</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
